--- a/data/input/複数シート型1_セクション別シート.xlsx
+++ b/data/input/複数シート型1_セクション別シート.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サンプリング設計" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト結果" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計・結論" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="キャプチャ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -255,6 +256,151 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -565,7 +711,11 @@
           <t>評価対象プロセス</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>売上プロセス</t>
+        </is>
+      </c>
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n"/>
@@ -579,7 +729,11 @@
           <t>評価対象期間</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2024年4月1日～2024年9月30日</t>
+        </is>
+      </c>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
@@ -593,7 +747,11 @@
           <t>コントロールID</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>CTRL-001</t>
+        </is>
+      </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
@@ -607,7 +765,11 @@
           <t>コントロール名称</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>売上計上承認</t>
+        </is>
+      </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
@@ -621,7 +783,11 @@
           <t>評価実施者</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>監査部 山田太郎</t>
+        </is>
+      </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
@@ -635,7 +801,11 @@
           <t>評価実施日</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>2024年10月15日</t>
+        </is>
+      </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
@@ -649,7 +819,11 @@
           <t>最終承認者</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>監査部長 鈴木花子</t>
+        </is>
+      </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
@@ -663,7 +837,11 @@
           <t>承認日</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2024年10月20日</t>
+        </is>
+      </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
@@ -719,7 +897,11 @@
           <t>母集団の定義</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2024年4月1日～9月30日に計上された売上取引（請求書ベース）</t>
+        </is>
+      </c>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
@@ -733,7 +915,11 @@
           <t>母集団件数</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2,450件</t>
+        </is>
+      </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
@@ -747,7 +933,11 @@
           <t>サンプリング方法</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>系統的サンプリング（毎月100件の母集団から4件を抽出）</t>
+        </is>
+      </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
@@ -779,7 +969,11 @@
           <t>サンプル抽出根拠</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>売上計上の正確性、網羅性、期間配分の評価が重要であり、月次での統制の有効性を確認する必要があるため、月次4件×6ヶ月=24件に加え、追加で1件を抽出</t>
+        </is>
+      </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
@@ -802,9 +996,9 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>正確性
-網羅性
-期間配分</t>
+          <t>売上の正確性（金額、数量、単価が正確であること）
+売上の網羅性（計上すべき売上がすべて計上されていること）
+売上の期間配分（売上が正しい期間に計上されていること）</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -822,9 +1016,9 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1. 請求書と会計システム上の計上データ（金額・数量・請求ID）の突合を行い、不一致がないことを確認する。
-2. 請求書の請求日・納品日と会計計上日が一致していること（日付一致確認）。
-3. 承認フロー（承認印／承認ログ）の存在を確認し、承認が適切に行われていることを検証する（承認確認）。</t>
+          <t>1. 抽出した売上取引について、請求書と売上計上データの金額、数量、単価が一致していることを確認
+2. 請求書の日付と売上計上日が一致していることを確認
+3. 売上計上が適切に承認されていることを確認（承認印の有無、承認者の確認）</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -842,11 +1036,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>請求書原本／請求書写し
-納品書（受領印または受領メール）
-会計システムの計上データ（計上伝票、仕訳出力）
-承認ログ／承認印（承認者、承認日が分かる証跡）
-システム記録（システム上の記録有無／記録内容）</t>
+          <t>請求書、売上計上システムの記録、承認フロー記録、納品書、契約書</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -878,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="18" customWidth="1" style="6" min="1" max="5"/>
@@ -911,7 +1101,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>テスト結果</t>
+          <t>テスト内容</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -922,6 +1112,16 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>その他</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>不備の性質</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>影響度</t>
         </is>
       </c>
     </row>
@@ -936,13 +1136,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -957,13 +1161,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -978,13 +1186,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -999,17 +1211,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>承認状況: 未承認; 備考: 承認印漏れ</t>
-        </is>
-      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>システム記録: 記録あり; 差異: 承認なし</t>
+          <t>承認未実施（承認印漏れ）</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>承認印漏れ、システム記録あり</t>
         </is>
       </c>
     </row>
@@ -1024,13 +1241,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1045,13 +1266,27 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>承認印がない</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>承認手続の遵守不足</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
     </row>
@@ -1066,13 +1301,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1087,13 +1326,17 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1108,13 +1351,17 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1376,17 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1150,13 +1401,17 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1426,17 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1192,13 +1451,17 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1476,17 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1234,13 +1501,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1255,13 +1526,17 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1276,13 +1551,17 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1297,13 +1576,17 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1318,13 +1601,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1626,17 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1360,13 +1651,17 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1381,13 +1676,17 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1402,13 +1701,17 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1423,13 +1726,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1444,13 +1751,17 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
+          <t>金額・日付・承認確認</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>備考: 標準取引; システム記録: 記録あり</t>
+          <t>標準取引で記録あり</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1856,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>無効</t>
+          <t>有効</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -1563,8 +1874,8 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>サンプル25件のうち1件（INV-2025-150）で承認が未実施（承認印漏れ、承認状況：未承認）という不備が確認されたため、統制が一貫して適切に運用されているとは言い切れません。監査上の判断基準として「サンプルごとのテストのうち1件でも不備が見られれば統制は有効とは言えない」ため、本統制は有効と評価できません。
-全体としては24/25件は適合しており、逸脱率は4.0%で許容逸脱率5%を下回る水準ですが、単一の承認漏れでも不正・誤記入・計上ミスのリスクが残る点が問題です。特に承認プロセスにおける物理的押印漏れや承認手順の履行漏れは、内部統制の信頼性を低下させるため、是正措置が必要と判断します。</t>
+          <t>25件のサンプルテストを実施した結果、24件が適合し、1件の軽微な不備（承認印の漏れ）が発見された。逸脱率は4.0%であり、許容逸脱率5%以下であることから、売上計上承認統制は全体として有効であると評価する。
+発見された不備は、承認フロー上での確認漏れと考えられ、システム上の強制的な承認フローの導入により改善可能である。</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -1582,10 +1893,10 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>1. 承認チェックリストの導入と運用（請求処理時に承認の有無を確実にチェックするフローを明文化し、処理担当がチェックリストに署名する）。
-2. 電子承認（ワークフロー）または承認ログの必須化と監査ログの定期レビュー（承認がシステム上で記録されるよう設定し、月次で抜取レビューを実施）。
-3. 担当者向けの再教育・運用トレーニングの実施（承認手順、証憑保管、突合作業の手順を再周知）。
-改善予定日：2026-03-31</t>
+          <t>1. 売上計上システムの承認フローを強制化し、承認なしには計上できないようにシステム設定を変更
+2. 承認者向けの研修を実施し、承認手続の重要性を周知
+3. 月次で承認漏れの有無を確認し、改善状況をモニタリング
+改善予定日：2024年11月30日</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -1604,4 +1915,21 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" style="6" min="1" max="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>